--- a/docs/Test_Report/Gpt/TestPlanExecutionReport.xlsx
+++ b/docs/Test_Report/Gpt/TestPlanExecutionReport.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Strategy Compliance'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -716,7 +716,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005,MCAL-27004</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2024-10-18 10:41:29.132056-05:00 CDT</t>
+          <t>2024-12-18 07:19:37.961029-06:00 CDT</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>67</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>84</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="inlineStr">
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
@@ -1420,7 +1420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U109"/>
+  <dimension ref="A1:U85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1556,32 +1556,32 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26288</t>
+          <t>MCAL-27017</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>GPT driver code build: GPT timers/ ISR type</t>
+          <t>Positive test case to validate the Gpt_EnableNotification() API in continuous mode</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Requirement,Requirement</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22040</t>
+          <t>MCAL-21433,MCAL-21432</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Test to check whether code is building correctly with all channels and all ISR types</t>
+          <t>Gpt_EnableNotification() API should not report  any errors and enable the timer channel requested for notifications in continuous mode</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1606,13 +1606,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test2",
+    "test_app_name": "Gpt_test3",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test2/Gpt_test2.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test3/Gpt_test3.out"
       }
     },
    "uart_input": {
@@ -1638,17 +1638,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>No Compilation errors should be observed</t>
+          <t>GPT timers 0,1 &amp; 2 should run with configured value and receive notification event</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Usability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Use Case Analysis</t>
+          <t>Requirements-Analysis</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
@@ -1687,22 +1687,22 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26287</t>
+          <t>MCAL-26288</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>GPT driver code build: GptDevErrorDetect  : On</t>
+          <t>GPT driver code build: GPT timers/ ISR type</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22045</t>
+          <t>MCAL-22040</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Test to check whether code is building correctly with GptDevErrorDetect is On</t>
+          <t>Test to check whether code is building correctly with all channels and all ISR types</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -1737,13 +1737,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test1",
+    "test_app_name": "Gpt_test2",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test2/Gpt_test2.out"
       }
     },
    "uart_input": {
@@ -1789,7 +1789,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>Full,Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
@@ -1818,22 +1818,22 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26286</t>
+          <t>MCAL-26287</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>GPT driver code build: GptDevErrorDetect  : Off</t>
+          <t>GPT driver code build: GptDevErrorDetect  : On</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Test to check whether code is building correctly with GptDevErrorDetect is Off</t>
+          <t>Test to check whether code is building correctly with GptDevErrorDetect is On</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -1868,13 +1868,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test5",
+    "test_app_name": "Gpt_test1",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
       }
     },
    "uart_input": {
@@ -1930,12 +1930,12 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
@@ -1949,22 +1949,22 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26283</t>
+          <t>MCAL-26286</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>GPT driver code build: GptTimeRemainingApi  : On</t>
+          <t>GPT driver code build: GptDevErrorDetect  : Off</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22061</t>
+          <t>MCAL-22045</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Test to check whether code is building correctly with GptTimeRemainingApi is On</t>
+          <t>Test to check whether code is building correctly with GptDevErrorDetect is Off</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -1999,13 +1999,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test1",
+    "test_app_name": "Gpt_test5",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
       }
     },
    "uart_input": {
@@ -2061,12 +2061,12 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
@@ -2080,22 +2080,22 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26282</t>
+          <t>MCAL-26283</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>GPT driver code build: GptTimeRemainingApi  : Off</t>
+          <t>GPT driver code build: GptTimeRemainingApi  : On</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Test to check whether code is building correctly with GptTimeRemainingApi is Off</t>
+          <t>Test to check whether code is building correctly with GptTimeRemainingApi is On</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -2130,13 +2130,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test5",
+    "test_app_name": "Gpt_test1",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
       }
     },
    "uart_input": {
@@ -2192,12 +2192,12 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
@@ -2211,22 +2211,22 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26281</t>
+          <t>MCAL-26282</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>GPT driver code build: GptTimeElapsedApi  : On</t>
+          <t>GPT driver code build: GptTimeRemainingApi  : Off</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22060</t>
+          <t>MCAL-22061</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Test to check whether code is building correctly with GptTimeElapsedApi is On</t>
+          <t>Test to check whether code is building correctly with GptTimeRemainingApi is Off</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -2261,13 +2261,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test1",
+    "test_app_name": "Gpt_test5",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
       }
     },
    "uart_input": {
@@ -2323,12 +2323,12 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr"/>
@@ -2342,22 +2342,22 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26280</t>
+          <t>MCAL-26281</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>GPT driver code build: GptTimeElapsedApi  : Off</t>
+          <t>GPT driver code build: GptTimeElapsedApi  : On</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Test to check whether code is building correctly with GptTimeElapsedApi is Off</t>
+          <t>Test to check whether code is building correctly with GptTimeElapsedApi is On</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -2392,13 +2392,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test5",
+    "test_app_name": "Gpt_test1",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
       }
     },
    "uart_input": {
@@ -2454,12 +2454,12 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr"/>
@@ -2473,22 +2473,22 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26279</t>
+          <t>MCAL-26280</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>GPT driver code build: GptEnableDisableNotificationApi  : On</t>
+          <t>GPT driver code build: GptTimeElapsedApi  : Off</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22059</t>
+          <t>MCAL-22060</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Test to check whether code is building correctly with GptEnableDisableNotificationApi is On</t>
+          <t>Test to check whether code is building correctly with GptTimeElapsedApi is Off</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -2523,13 +2523,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test1",
+    "test_app_name": "Gpt_test5",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
       }
     },
    "uart_input": {
@@ -2585,12 +2585,12 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr"/>
@@ -2604,22 +2604,22 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26278</t>
+          <t>MCAL-26279</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>GPT driver code build: GptEnableDisableNotificationApi  : Off</t>
+          <t>GPT driver code build: GptEnableDisableNotificationApi  : On</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Test to check whether code is building correctly with GptEnableDisableNotificationApi is Off</t>
+          <t>Test to check whether code is building correctly with GptEnableDisableNotificationApi is On</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -2654,13 +2654,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test5",
+    "test_app_name": "Gpt_test1",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
       }
     },
    "uart_input": {
@@ -2716,12 +2716,12 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr"/>
@@ -2735,22 +2735,22 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26277</t>
+          <t>MCAL-26278</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>GPT driver code build: GptDeinitApi : On</t>
+          <t>GPT driver code build: GptEnableDisableNotificationApi  : Off</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22058</t>
+          <t>MCAL-22059</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Test to check whether code is building correctly with GptDeinitApi is On</t>
+          <t>Test to check whether code is building correctly with GptEnableDisableNotificationApi is Off</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -2785,13 +2785,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test1",
+    "test_app_name": "Gpt_test5",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
       }
     },
    "uart_input": {
@@ -2847,12 +2847,12 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr"/>
@@ -2866,22 +2866,22 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26276</t>
+          <t>MCAL-26277</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>GPT driver code build: GptDeinitApi : Off</t>
+          <t>GPT driver code build: GptDeinitApi : On</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Test to check whether code is building correctly with GptDeinitApi is Off</t>
+          <t>Test to check whether code is building correctly with GptDeinitApi is On</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -2916,13 +2916,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test5",
+    "test_app_name": "Gpt_test1",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
       }
     },
    "uart_input": {
@@ -2978,12 +2978,12 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr"/>
@@ -2997,22 +2997,22 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26275</t>
+          <t>MCAL-26276</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>GPT driver code build: GptVersionInfoApi : On</t>
+          <t>GPT driver code build: GptDeinitApi : Off</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22062</t>
+          <t>MCAL-22058</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Test to check whether code is building correctly with GptVersionInfoApi is On</t>
+          <t>Test to check whether code is building correctly with GptDeinitApi is Off</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -3047,13 +3047,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test1",
+    "test_app_name": "Gpt_test5",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
       }
     },
    "uart_input": {
@@ -3109,12 +3109,12 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr"/>
@@ -3128,22 +3128,22 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26274</t>
+          <t>MCAL-26275</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>GPT driver code build: GptVersionInfoApi : Off</t>
+          <t>GPT driver code build: GptVersionInfoApi : On</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Test to check whether code is building correctly with GptVersionInfoApi is Off</t>
+          <t>Test to check whether code is building correctly with GptVersionInfoApi is On</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -3178,13 +3178,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test5",
+    "test_app_name": "Gpt_test1",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
       }
     },
    "uart_input": {
@@ -3240,12 +3240,12 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
@@ -3259,22 +3259,22 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26273</t>
+          <t>MCAL-26274</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_DisableNotification() API  whether it is configurable On/Off by the configuration parameter</t>
+          <t>GPT driver code build: GptVersionInfoApi : Off</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22030</t>
+          <t>MCAL-22062</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_DisableNotification() API  whether it is configurable On/Off by the configuration parameter</t>
+          <t>Test to check whether code is building correctly with GptVersionInfoApi is Off</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Check manually in the driver code whether it is pre compile time configurable On/Off by the configuration parameter</t>
+          <t>No Compilation errors should be observed</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Usability</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>Requirements-Analysis</t>
+          <t>Use Case Analysis</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
@@ -3390,32 +3390,32 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26271</t>
+          <t>MCAL-26273</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_DisableNotification() API when timer channel is not in UNINIT state</t>
+          <t>Validate the Gpt_DisableNotification() API  whether it is configurable On/Off by the configuration parameter</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22083,MCAL-22028,MCAL-22059</t>
+          <t>MCAL-22030</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_DisableNotification() API  by calling Gpt_DisableNotification() API when timer channel is not in UNINIT state</t>
+          <t>Validate the Gpt_DisableNotification() API  whether it is configurable On/Off by the configuration parameter</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -3440,13 +3440,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test1",
+    "test_app_name": "Gpt_test5",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
       }
     },
    "uart_input": {
@@ -3472,7 +3472,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Gpt driver should disable the interrupt notification for the requested channel</t>
+          <t>Check manually in the driver code whether it is pre compile time configurable On/Off by the configuration parameter</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr"/>
@@ -3521,32 +3521,32 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26269</t>
+          <t>MCAL-26271</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_DisableNotification() API when requested with invalid channel</t>
+          <t>Positive testcase to validate the Gpt_DisableNotification() API when timer channel is not in UNINIT state</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design,Design</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22032</t>
+          <t>MCAL-22083,MCAL-22028,MCAL-22059</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_DisableNotification() API  by calling Gpt_DisableNotification() when requested with invalid channel</t>
+          <t>Validate the Gpt_DisableNotification() API  by calling Gpt_DisableNotification() API when timer channel is not in UNINIT state</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_PARAM_CHANNEL" error should be detected and reported to DET module</t>
+          <t>Gpt driver should disable the interrupt notification for the requested channel</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Fault Injection</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr"/>
@@ -3652,22 +3652,22 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26268</t>
+          <t>MCAL-26270</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_DisableNotification() API when driver is not in INIT state</t>
+          <t>Negative testcase to validate the Gpt_DisableNotification() API when notification callback pointer is NULL</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22031</t>
+          <t>MCAL-22033</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_DisableNotification() API  by calling Gpt_DisableNotification() API before Gpt_Init() API</t>
+          <t>Validate the Gpt_DisableNotification() API  by calling Gpt_DisableNotification() API when notification callback pointer is NULL</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -3702,13 +3702,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test1",
+    "test_app_name": "Gpt_test4",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test4/Gpt_test4.out"
       }
     },
    "uart_input": {
@@ -3734,7 +3734,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_UNINIT" error should be detected and reported to DET module</t>
+          <t>"GPT_E_PARAM_CHANNEL"  error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr"/>
@@ -3783,22 +3783,22 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26267</t>
+          <t>MCAL-26269</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_EnableNotification() API  whether it is configurable On/Off by the configuration parameter</t>
+          <t>Negative testcase to validate the Gpt_DisableNotification() API when requested with invalid channel</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22024</t>
+          <t>MCAL-22032</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_EnableNotification() API  whether it is configurable On/Off by the configuration parameter</t>
+          <t>Validate the Gpt_DisableNotification() API  by calling Gpt_DisableNotification() when requested with invalid channel</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -3833,13 +3833,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test5",
+    "test_app_name": "Gpt_test1",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
       }
     },
    "uart_input": {
@@ -3865,12 +3865,12 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Check manually in the driver code whether it is pre compile time configurable On/Off by the configuration parameter</t>
+          <t>"GPT_E_PARAM_CHANNEL" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Fault Injection</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>Full,Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr"/>
@@ -3914,32 +3914,32 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26265</t>
+          <t>MCAL-26268</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_EnableNotification() API when timer channel is not in UNINIT state</t>
+          <t>Negative testcase to validate the Gpt_DisableNotification() API when driver is not in INIT state</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22055,MCAL-22082,MCAL-22022,MCAL-22059</t>
+          <t>MCAL-22031</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_EnableNotification() API  by calling Gpt_EnableNotification() API when timer channel is not in UNINIT state</t>
+          <t>Validate the Gpt_DisableNotification() API  by calling Gpt_DisableNotification() API before Gpt_Init() API</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Gpt driver should enable the interrupt notification for the requested channel</t>
+          <t>"GPT_E_UNINIT" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Fault Injection</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr"/>
@@ -4045,22 +4045,22 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26264</t>
+          <t>MCAL-26267</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_EnableNotification() API when notification callback pointer is NULL</t>
+          <t>Validate the Gpt_EnableNotification() API  whether it is configurable On/Off by the configuration parameter</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22027</t>
+          <t>MCAL-22024</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_EnableNotification() API  by calling Gpt_EnableNotification() API when notification callback pointer is NULL</t>
+          <t>Validate the Gpt_EnableNotification() API  whether it is configurable On/Off by the configuration parameter</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -4095,13 +4095,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test4",
+    "test_app_name": "Gpt_test5",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test4/Gpt_test4.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
       }
     },
    "uart_input": {
@@ -4127,12 +4127,12 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_PARAM_CHANNEL"  error should be detected and reported to DET module</t>
+          <t>Check manually in the driver code whether it is pre compile time configurable On/Off by the configuration parameter</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Fault Injection</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr"/>
@@ -4176,32 +4176,32 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26263</t>
+          <t>MCAL-26265</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_EnableNotification() API when requested with invalid channel</t>
+          <t>Positive testcase to validate the Gpt_EnableNotification() API when timer channel is not in UNINIT state</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design,Design,Design</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22026</t>
+          <t>MCAL-22055,MCAL-22082,MCAL-22022,MCAL-22059</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_EnableNotification() API  by calling Gpt_EnableNotification() when requested with invalid channel</t>
+          <t>Validate the Gpt_EnableNotification() API  by calling Gpt_EnableNotification() API when timer channel is not in UNINIT state</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_PARAM_CHANNEL" error should be detected and reported to DET module</t>
+          <t>Gpt driver should enable the interrupt notification for the requested channel</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Fault Injection</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr"/>
@@ -4307,22 +4307,22 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26262</t>
+          <t>MCAL-26264</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_EnableNotification() API when driver is not in INIT state</t>
+          <t>Negative testcase to validate the Gpt_EnableNotification() API when notification callback pointer is NULL</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22025</t>
+          <t>MCAL-22027</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_EnableNotification() API  by calling Gpt_EnableNotification() API before Gpt_Init() API</t>
+          <t>Validate the Gpt_EnableNotification() API  by calling Gpt_EnableNotification() API when notification callback pointer is NULL</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -4357,13 +4357,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test1",
+    "test_app_name": "Gpt_test4",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test4/Gpt_test4.out"
       }
     },
    "uart_input": {
@@ -4389,7 +4389,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_UNINIT" error should be detected and reported to DET module</t>
+          <t>"GPT_E_PARAM_CHANNEL"  error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -4438,32 +4438,32 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26260</t>
+          <t>MCAL-26263</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_StopTimer() API when timer channel is not in RUNNING state</t>
+          <t>Negative testcase to validate the Gpt_EnableNotification() API when requested with invalid channel</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22017,MCAL-22018</t>
+          <t>MCAL-22026</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_StopTimer() API  by calling Gpt_StopTimer() API when timer channel is in not RUNNING state</t>
+          <t>Validate the Gpt_EnableNotification() API  by calling Gpt_EnableNotification() when requested with invalid channel</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Gpt driver should return without stopping the timer</t>
+          <t>"GPT_E_PARAM_CHANNEL" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>Full,Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr"/>
@@ -4569,32 +4569,32 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26259</t>
+          <t>MCAL-26262</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_StopTimer() API when timer channel is in RUNNING state</t>
+          <t>Negative testcase to validate the Gpt_EnableNotification() API when driver is not in INIT state</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22015,MCAL-22016,MCAL-22081</t>
+          <t>MCAL-22025</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_StopTimer() API  by calling Gpt_StopTimer() API when timer channel is in RUNNING state</t>
+          <t>Validate the Gpt_EnableNotification() API  by calling Gpt_EnableNotification() API before Gpt_Init() API</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>Gpt driver should stop the timer and return without any errors</t>
+          <t>"GPT_E_UNINIT" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>Full,Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr"/>
@@ -4700,32 +4700,32 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26258</t>
+          <t>MCAL-26260</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_StopTimer() API when requested with invalid channel</t>
+          <t>Negative testcase to validate the Gpt_StopTimer() API when timer channel is not in RUNNING state</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22020</t>
+          <t>MCAL-22017,MCAL-22018</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_StopTimer() API  by calling Gpt_StopTimer() when requested with invalid channel</t>
+          <t>Validate the Gpt_StopTimer() API  by calling Gpt_StopTimer() API when timer channel is in not RUNNING state</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_PARAM_CHANNEL" error should be detected and reported to DET module</t>
+          <t>Gpt driver should return without stopping the timer</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr"/>
@@ -4831,32 +4831,32 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26257</t>
+          <t>MCAL-26259</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_StopTimer() API when driver is not in INIT state</t>
+          <t>Negative testcase to validate the Gpt_StopTimer() API when timer channel is in RUNNING state</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design,Design</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22021</t>
+          <t>MCAL-22015,MCAL-22016,MCAL-22081</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_StopTimer() API  by calling Gpt_StopTimer() API before Gpt_Init() API</t>
+          <t>Validate the Gpt_StopTimer() API  by calling Gpt_StopTimer() API when timer channel is in RUNNING state</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_UNINIT" error should be detected and reported to DET module</t>
+          <t>Gpt driver should stop the timer and return without any errors</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -4943,12 +4943,12 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr"/>
@@ -4962,32 +4962,32 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26255</t>
+          <t>MCAL-26258</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_StartTimer() API when timer channel is in INIT state</t>
+          <t>Negative testcase to validate the Gpt_StopTimer() API when requested with invalid channel</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design,Design,Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22037,MCAL-22007,MCAL-21960,MCAL-22080,MCAL-21956,MCAL-22008</t>
+          <t>MCAL-22020</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_StartTimer() API  by calling Gpt_StartTimer() API when timer channel is in INIT state</t>
+          <t>Validate the Gpt_StopTimer() API  by calling Gpt_StopTimer() when requested with invalid channel</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -5044,12 +5044,12 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Gpt driver should start the timer with defined target time and user should be notified when time elapsed</t>
+          <t>"GPT_E_PARAM_CHANNEL" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Fault Injection</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr"/>
@@ -5093,32 +5093,32 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26254</t>
+          <t>MCAL-26257</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_StartTimer() API when timer channel is in RUNNING state</t>
+          <t>Negative testcase to validate the Gpt_StopTimer() API when driver is not in INIT state</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22010,MCAL-22014</t>
+          <t>MCAL-22021</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_StartTimer() API  by calling Gpt_StartTimer() API when timer channel is in RUNNING state</t>
+          <t>Validate the Gpt_StopTimer() API  by calling Gpt_StopTimer() API before Gpt_Init() API</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_BUSY" runtime error should be detected and reported to DET module</t>
+          <t>"GPT_E_UNINIT" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr"/>
@@ -5224,32 +5224,32 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26253</t>
+          <t>MCAL-26255</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_StartTimer() API when requested with invalid channel</t>
+          <t>Positive testcase to validate the Gpt_StartTimer() API when timer channel is in INIT state</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design,Design,Design,Design,Design</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22011</t>
+          <t>MCAL-22037,MCAL-22007,MCAL-21960,MCAL-22080,MCAL-21956,MCAL-22008</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_StartTimer() API  by calling Gpt_StartTimer() when requested with invalid channel</t>
+          <t>Validate the Gpt_StartTimer() API  by calling Gpt_StartTimer() API when timer channel is in INIT state</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_PARAM_CHANNEL" error should be detected and reported to DET module</t>
+          <t>Gpt driver should start the timer with defined target time and user should be notified when time elapsed</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Fault Injection</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr"/>
@@ -5355,32 +5355,32 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26252</t>
+          <t>MCAL-26254</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_StartTimer() API when count value as 0</t>
+          <t>Negative testcase to validate the Gpt_StartTimer() API when timer channel is in RUNNING state</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22012</t>
+          <t>MCAL-22010,MCAL-22014</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_StartTimer() API  by calling Gpt_StartTimer() whencount value as 0</t>
+          <t>Validate the Gpt_StartTimer() API  by calling Gpt_StartTimer() API when timer channel is in RUNNING state</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_PARAM_CHANNEL" error should be detected and reported to DET module</t>
+          <t>"GPT_E_BUSY" runtime error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr"/>
@@ -5486,22 +5486,22 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26251</t>
+          <t>MCAL-26253</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_StartTimer() API when driver is not in INIT state</t>
+          <t>Negative testcase to validate the Gpt_StartTimer() API when requested with invalid channel</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22013</t>
+          <t>MCAL-22011</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_StartTimer() API  by calling Gpt_StartTimer() API before Gpt_Init() API</t>
+          <t>Validate the Gpt_StartTimer() API  by calling Gpt_StartTimer() when requested with invalid channel</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_UNINIT" error should be detected and reported to DET module</t>
+          <t>"GPT_E_PARAM_CHANNEL" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
@@ -5617,22 +5617,22 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26249</t>
+          <t>MCAL-26252</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeRemaining() API  whether it is configurable On/Off by the configuration parameter</t>
+          <t>Negative testcase to validate the Gpt_StartTimer() API when count value as 0</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22004</t>
+          <t>MCAL-22012</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeRemaining() API  whether it is configurable On/Off by the configuration parameter</t>
+          <t>Validate the Gpt_StartTimer() API  by calling Gpt_StartTimer() whencount value as 0</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -5667,13 +5667,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test5",
+    "test_app_name": "Gpt_test1",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
       }
     },
    "uart_input": {
@@ -5699,12 +5699,12 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>Check manually in the driver code whether it is pre compile time configurable On/Off by the configuration parameter</t>
+          <t>"GPT_E_PARAM_CHANNEL" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Fault Injection</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>Full,Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr"/>
@@ -5748,22 +5748,22 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26248</t>
+          <t>MCAL-26251</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in UNINITIALIZED state &amp; timer mode is continuous</t>
+          <t>Negative testcase to validate the Gpt_StartTimer() API when driver is not in INIT state</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22005</t>
+          <t>MCAL-22013</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in UNINITIALIZED state and timer mode is continuous</t>
+          <t>Validate the Gpt_StartTimer() API  by calling Gpt_StartTimer() API before Gpt_Init() API</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -5798,13 +5798,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test3",
+    "test_app_name": "Gpt_test1",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test3/Gpt_test3.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
       }
     },
    "uart_input": {
@@ -5830,12 +5830,12 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeRemaining() API should return 0</t>
+          <t>"GPT_E_UNINIT" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Fault Injection</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr"/>
@@ -5879,22 +5879,22 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26247</t>
+          <t>MCAL-26249</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in STOPPED state &amp; timer mode is continuous</t>
+          <t>Validate the Gpt_GetTimeRemaining() API  whether it is configurable On/Off by the configuration parameter</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22001</t>
+          <t>MCAL-22004</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in STOPPED state and timer mode is continuous</t>
+          <t>Validate the Gpt_GetTimeRemaining() API  whether it is configurable On/Off by the configuration parameter</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -5929,13 +5929,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test3",
+    "test_app_name": "Gpt_test5",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test3/Gpt_test3.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
       }
     },
    "uart_input": {
@@ -5961,7 +5961,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeRemaining() API should return the elapsed time</t>
+          <t>Check manually in the driver code whether it is pre compile time configurable On/Off by the configuration parameter</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr"/>
@@ -6010,22 +6010,22 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26246</t>
+          <t>MCAL-26248</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in RUNNING state &amp; timer mode is continuous</t>
+          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in UNINITIALIZED state &amp; timer mode is continuous</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21999</t>
+          <t>MCAL-22005</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in RUNNING state and timer mode is continuous</t>
+          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in UNINITIALIZED state and timer mode is continuous</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeRemaining() API should return the elapsed time</t>
+          <t>Gpt_GetTimeRemaining() API should return 0</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr"/>
@@ -6141,32 +6141,32 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26245</t>
+          <t>MCAL-26247</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in INIT state &amp; timer mode is continuous</t>
+          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in STOPPED state &amp; timer mode is continuous</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21958,MCAL-22000,MCAL-21999</t>
+          <t>MCAL-22001</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in INIT state and timer mode is continuous</t>
+          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in STOPPED state and timer mode is continuous</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeRemaining() API should return 0</t>
+          <t>Gpt_GetTimeRemaining() API should return the elapsed time</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>Full,Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr"/>
@@ -6272,22 +6272,22 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26244</t>
+          <t>MCAL-26246</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in UNINITIALIZED state &amp; timer mode is one shot</t>
+          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in RUNNING state &amp; timer mode is continuous</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22005</t>
+          <t>MCAL-21999</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in UNINITIALIZED state and timer mode is one shot</t>
+          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in RUNNING state and timer mode is continuous</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -6322,13 +6322,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test1",
+    "test_app_name": "Gpt_test3",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test3/Gpt_test3.out"
       }
     },
    "uart_input": {
@@ -6354,7 +6354,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeRemaining() API should return 0</t>
+          <t>Gpt_GetTimeRemaining() API should return the elapsed time</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr"/>
@@ -6403,32 +6403,32 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26243</t>
+          <t>MCAL-26245</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in EXPIRED state &amp; timer mode is one shot mode</t>
+          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in INIT state &amp; timer mode is continuous</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Design,Design</t>
+          <t>Design,Design,Design</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22002,MCAL-21957</t>
+          <t>MCAL-21958,MCAL-22000,MCAL-21999</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in EXPIRED state and timer mode is one shot</t>
+          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in INIT state and timer mode is continuous</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -6453,13 +6453,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test1",
+    "test_app_name": "Gpt_test3",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test3/Gpt_test3.out"
       }
     },
    "uart_input": {
@@ -6505,7 +6505,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -6515,12 +6515,12 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
@@ -6534,32 +6534,32 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26242</t>
+          <t>MCAL-26244</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in STOPPED state &amp; timer mode is one shot mode</t>
+          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in UNINITIALIZED state &amp; timer mode is one shot</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21993,MCAL-22001</t>
+          <t>MCAL-22005</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in STOPPED state and timer mode is one shot</t>
+          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in UNINITIALIZED state and timer mode is one shot</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeRemaining() API should return the elapsed time</t>
+          <t>Gpt_GetTimeRemaining() API should return 0</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr"/>
@@ -6665,32 +6665,32 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26241</t>
+          <t>MCAL-26243</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in RUNNING state &amp; timer mode is one shot mode</t>
+          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in EXPIRED state &amp; timer mode is one shot mode</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21999</t>
+          <t>MCAL-22002,MCAL-21957</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in RUNNING state and timer mode is one shot</t>
+          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in EXPIRED state and timer mode is one shot</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeRemaining() API should return the elapsed time</t>
+          <t>Gpt_GetTimeRemaining() API should return 0</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr"/>
@@ -6796,32 +6796,32 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26240</t>
+          <t>MCAL-26242</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in INIT state &amp; timer mode is one shot mode</t>
+          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in STOPPED state &amp; timer mode is one shot mode</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design,Design</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21999,MCAL-22073,MCAL-22061,MCAL-22000</t>
+          <t>MCAL-21993,MCAL-22001</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in INIT state and timer mode is one shot</t>
+          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in STOPPED state and timer mode is one shot</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeRemaining() API should return 0</t>
+          <t>Gpt_GetTimeRemaining() API should return the elapsed time</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>Full,Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -6927,22 +6927,22 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26239</t>
+          <t>MCAL-26241</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_GetTimeRemaining() API with invalid channel id</t>
+          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in RUNNING state &amp; timer mode is one shot mode</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22006</t>
+          <t>MCAL-21999</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() API with invalid channel id</t>
+          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in RUNNING state and timer mode is one shot</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_PARAM_CHANNEL" error should be detected and reported to DET module</t>
+          <t>Gpt_GetTimeRemaining() API should return the elapsed time</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Fault Injection</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr"/>
@@ -7058,32 +7058,32 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26238</t>
+          <t>MCAL-26240</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_GetTimeRemaining() API when driver is not in INIT state</t>
+          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in INIT state &amp; timer mode is one shot mode</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design,Design,Design</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22005</t>
+          <t>MCAL-21999,MCAL-22073,MCAL-22061,MCAL-22000</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeElapsed() API before Gpt_Init() API</t>
+          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() when timer channel in INIT state and timer mode is one shot</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_UNINIT" error should be detected and reported to DET module</t>
+          <t>Gpt_GetTimeRemaining() API should return 0</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Fault Injection</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr"/>
@@ -7189,22 +7189,22 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26236</t>
+          <t>MCAL-26239</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeElapsed() API  whether it is configurable On/Off by the configuration parameter</t>
+          <t>Negative testcase to validate the Gpt_GetTimeRemaining() API with invalid channel id</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21996</t>
+          <t>MCAL-22006</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeElapsed() API  whether it is configurable On/Off by the configuration parameter</t>
+          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeRemaining() API with invalid channel id</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -7239,13 +7239,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test5",
+    "test_app_name": "Gpt_test1",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
       }
     },
    "uart_input": {
@@ -7271,12 +7271,12 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>Check manually in the driver code whether it is pre compile time configurable On/Off by the configuration parameter</t>
+          <t>"GPT_E_PARAM_CHANNEL" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Fault Injection</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>Full,Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr"/>
@@ -7320,22 +7320,22 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26235</t>
+          <t>MCAL-26238</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in UNINITIALIZED state &amp; timer mode is continuous</t>
+          <t>Negative testcase to validate the Gpt_GetTimeRemaining() API when driver is not in INIT state</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21997</t>
+          <t>MCAL-22005</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in UNINITIALIZED state and timer mode is continuous</t>
+          <t>Validate the Gpt_GetTimeRemaining() API  by calling Gpt_GetTimeElapsed() API before Gpt_Init() API</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -7370,13 +7370,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test3",
+    "test_app_name": "Gpt_test1",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test3/Gpt_test3.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
       }
     },
    "uart_input": {
@@ -7402,12 +7402,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeElapsed() API should return 0</t>
+          <t>"GPT_E_UNINIT" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Fault Injection</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr"/>
@@ -7451,22 +7451,22 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26234</t>
+          <t>MCAL-26236</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in STOPPED state &amp; timer mode is continuous</t>
+          <t>Validate the Gpt_GetTimeElapsed() API  whether it is configurable On/Off by the configuration parameter</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21993</t>
+          <t>MCAL-21996</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in STOPPED state and timer mode is continuous</t>
+          <t>Validate the Gpt_GetTimeElapsed() API  whether it is configurable On/Off by the configuration parameter</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -7501,13 +7501,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test3",
+    "test_app_name": "Gpt_test5",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test3/Gpt_test3.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
       }
     },
    "uart_input": {
@@ -7533,7 +7533,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeElapsed() API should return the elapsed time</t>
+          <t>Check manually in the driver code whether it is pre compile time configurable On/Off by the configuration parameter</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
@@ -7563,12 +7563,12 @@
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr"/>
@@ -7582,22 +7582,22 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26233</t>
+          <t>MCAL-26235</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in RUNNING state &amp; timer mode is continuous</t>
+          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in UNINITIALIZED state &amp; timer mode is continuous</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21991</t>
+          <t>MCAL-21997</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in RUNNING state and timer mode is continuous</t>
+          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in UNINITIALIZED state and timer mode is continuous</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeElapsed() API should return the elapsed time</t>
+          <t>Gpt_GetTimeElapsed() API should return 0</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr"/>
@@ -7713,32 +7713,32 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26232</t>
+          <t>MCAL-26234</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in INIT state &amp; timer mode is continuous</t>
+          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in STOPPED state &amp; timer mode is continuous</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21991,MCAL-22078,MCAL-21992</t>
+          <t>MCAL-21993</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in INIT state and timer mode is continuous</t>
+          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in STOPPED state and timer mode is continuous</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeElapsed() API should return 0</t>
+          <t>Gpt_GetTimeElapsed() API should return the elapsed time</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>Full,Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr"/>
@@ -7844,22 +7844,22 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26231</t>
+          <t>MCAL-26233</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in UNINITIALIZED state &amp; timer mode is one shot</t>
+          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in RUNNING state &amp; timer mode is continuous</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21997</t>
+          <t>MCAL-21991</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in UNINITIALIZED state and timer mode is one shot</t>
+          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in RUNNING state and timer mode is continuous</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -7894,13 +7894,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test1",
+    "test_app_name": "Gpt_test3",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test3/Gpt_test3.out"
       }
     },
    "uart_input": {
@@ -7926,7 +7926,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeElapsed() API should return 0</t>
+          <t>Gpt_GetTimeElapsed() API should return the elapsed time</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr"/>
@@ -7975,32 +7975,32 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26230</t>
+          <t>MCAL-26232</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in EXPIRED state &amp; timer mode is one shot mode</t>
+          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in INIT state &amp; timer mode is continuous</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Design,Design</t>
+          <t>Design,Design,Design</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21994,MCAL-21957</t>
+          <t>MCAL-21991,MCAL-22078,MCAL-21992</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in EXPIRED state and timer mode is one shot</t>
+          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in INIT state and timer mode is continuous</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -8025,13 +8025,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test1",
+    "test_app_name": "Gpt_test3",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test3/Gpt_test3.out"
       }
     },
    "uart_input": {
@@ -8057,7 +8057,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeElapsed() API should return the elapsed time</t>
+          <t>Gpt_GetTimeElapsed() API should return 0</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr"/>
@@ -8106,22 +8106,22 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26229</t>
+          <t>MCAL-26231</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in STOPPED state &amp; timer mode is one shot mode</t>
+          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in UNINITIALIZED state &amp; timer mode is one shot</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21993</t>
+          <t>MCAL-21997</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in STOPPED state and timer mode is one shot</t>
+          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in UNINITIALIZED state and timer mode is one shot</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeRemaining() API should return the remaining time</t>
+          <t>Gpt_GetTimeElapsed() API should return 0</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr"/>
@@ -8237,32 +8237,32 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26228</t>
+          <t>MCAL-26230</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in RUNNING state &amp; timer mode is one shot mode</t>
+          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in EXPIRED state &amp; timer mode is one shot mode</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21991</t>
+          <t>MCAL-21994,MCAL-21957</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in RUNNING state and timer mode is one shot</t>
+          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in EXPIRED state and timer mode is one shot</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr"/>
@@ -8368,32 +8368,32 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26227</t>
+          <t>MCAL-26229</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in INIT state &amp; timer mode is one shot mode</t>
+          <t>Positive testcase to validate the Gpt_GetTimeRemaining() API when channel is in STOPPED state &amp; timer mode is one shot mode</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22079,MCAL-21990,MCAL-21992</t>
+          <t>MCAL-21993</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in INIT state and timer mode is one shot</t>
+          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in STOPPED state and timer mode is one shot</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeElapsed() API should return 0</t>
+          <t>Gpt_GetTimeRemaining() API should return the remaining time</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>Full,Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
@@ -8480,12 +8480,12 @@
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr"/>
@@ -8499,22 +8499,22 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26226</t>
+          <t>MCAL-26228</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_GetTimeElapsed() API with invalid channel id</t>
+          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in RUNNING state &amp; timer mode is one shot mode</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21998</t>
+          <t>MCAL-21991</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() API with invalid channel id</t>
+          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in RUNNING state and timer mode is one shot</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_PARAM_CHANNEL" error should be detected and reported to DET module</t>
+          <t>Gpt_GetTimeElapsed() API should return the elapsed time</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Fault Injection</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr"/>
@@ -8630,32 +8630,32 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26225</t>
+          <t>MCAL-26227</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_GetTimeElapsed() API when driver is not in INIT state</t>
+          <t>Positive testcase to validate the Gpt_GetTimeElapsed() API when channel is in INIT state &amp; timer mode is one shot mode</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design,Design</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21997</t>
+          <t>MCAL-22079,MCAL-21990,MCAL-21992</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() API before Gpt_Init() API</t>
+          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() when timer channel in INIT state and timer mode is one shot</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_UNINIT" error should be detected and reported to DET module</t>
+          <t>Gpt_GetTimeElapsed() API should return 0</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Fault Injection</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr"/>
@@ -8761,22 +8761,22 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26224</t>
+          <t>MCAL-26226</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_DeInit() API  whether it is configurable On/Off by the configuration parameter</t>
+          <t>Negative testcase to validate the Gpt_GetTimeElapsed() API with invalid channel id</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21986</t>
+          <t>MCAL-21998</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_DeInit() API  whether it is configurable On/Off by the configuration parameter</t>
+          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() API with invalid channel id</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -8811,13 +8811,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test5",
+    "test_app_name": "Gpt_test1",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
       }
     },
    "uart_input": {
@@ -8843,12 +8843,12 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>Check manually in the driver code whether it is pre compile time configurable On/Off by the configuration parameter</t>
+          <t>"GPT_E_PARAM_CHANNEL" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Fault Injection</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>Full,Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr"/>
@@ -8892,32 +8892,32 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26223</t>
+          <t>MCAL-26225</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_DeInit() API when input is a valid config pointer and all configuration data is valid</t>
+          <t>Negative testcase to validate the Gpt_GetTimeElapsed() API when driver is not in INIT state</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21983,MCAL-21984,MCAL-21987,MCAL-23351,MCAL-22083,MCAL-22074,MCAL-23357,MCAL-23350,MCAL-21982,MCAL-22076</t>
+          <t>MCAL-21997</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>Validate whether Gpt_DeInit() API deinitialise all the channels</t>
+          <t>Validate the Gpt_GetTimeElapsed() API  by calling Gpt_GetTimeElapsed() API before Gpt_Init() API</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -8942,13 +8942,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test2",
+    "test_app_name": "Gpt_test1",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test2/Gpt_test2.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
       }
     },
    "uart_input": {
@@ -8974,12 +8974,12 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>Gpt driver should be deinitialized without any error reporting</t>
+          <t>"GPT_E_UNINIT" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Fault Injection</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr"/>
@@ -9023,22 +9023,22 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26222</t>
+          <t>MCAL-26224</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_DeInit() API when one of the timer configured channel still in running state</t>
+          <t>Validate the Gpt_DeInit() API  whether it is configurable On/Off by the configuration parameter</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21988</t>
+          <t>MCAL-21986</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_DeInit() API  when one of the timer configured channel still in running state</t>
+          <t>Validate the Gpt_DeInit() API  whether it is configurable On/Off by the configuration parameter</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -9073,13 +9073,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test1",
+    "test_app_name": "Gpt_test5",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test5/Gpt_test5.out"
       }
     },
    "uart_input": {
@@ -9105,12 +9105,12 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_BUSY" runtime error should be detected and reported to DET module</t>
+          <t>Check manually in the driver code whether it is pre compile time configurable On/Off by the configuration parameter</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>Fault Injection</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr"/>
@@ -9154,32 +9154,32 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26221</t>
+          <t>MCAL-26223</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_DeInit() API when Gpt driver is not in INIT state</t>
+          <t>Positive testcase to validate the Gpt_DeInit() API when input is a valid config pointer and all configuration data is valid</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21989</t>
+          <t>MCAL-21983,MCAL-21984,MCAL-21987,MCAL-23351,MCAL-22083,MCAL-22074,MCAL-23357,MCAL-23350,MCAL-21982,MCAL-22076</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_DeInit() API  by calling Gpt_DeInit() API before Gpt_Init() API</t>
+          <t>Validate whether Gpt_DeInit() API deinitialise all the channels</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -9204,13 +9204,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test1",
+    "test_app_name": "Gpt_test2",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test2/Gpt_test2.out"
       }
     },
    "uart_input": {
@@ -9236,12 +9236,12 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_UNINIT" error should be detected and reported to DET module</t>
+          <t>Gpt driver should be deinitialized without any error reporting</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>Fault Injection</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr"/>
@@ -9285,32 +9285,32 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26220</t>
+          <t>MCAL-26222</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Positive testcase to validate the Gpt_Init() API when input is a valid config pointer and all configuration data is valid</t>
+          <t>Negative testcase to validate the Gpt_DeInit() API when one of the timer configured channel still in running state</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-23354,MCAL-21985,MCAL-21973,MCAL-22051,MCAL-21975,MCAL-21972,MCAL-22049,MCAL-22068,MCAL-21976,MCAL-21978,MCAL-23357,MCAL-22072,MCAL-22083,MCAL-21974,MCAL-22075,MCAL-23356,MCAL-22050,MCAL-22067,MCAL-22070,MCAL-22057,MCAL-22069,MCAL-23358,MCAL-23352,MCAL-22071,MCAL-21977,MCAL-21979</t>
+          <t>MCAL-21988</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_Init() API  by passing a valid config pointer and all configuration data is valid</t>
+          <t>Validate the Gpt_DeInit() API  when one of the timer configured channel still in running state</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -9335,13 +9335,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test2",
+    "test_app_name": "Gpt_test1",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test2/Gpt_test2.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
       }
     },
    "uart_input": {
@@ -9367,12 +9367,12 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>Gpt driver should initialize all the configured channels</t>
+          <t>"GPT_E_BUSY" runtime error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Fault Injection</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -9397,12 +9397,12 @@
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr"/>
@@ -9416,22 +9416,22 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26219</t>
+          <t>MCAL-26221</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_Init() API when input is a valid config pointer but one of the channel id is inavlid(not supported channel)</t>
+          <t>Negative testcase to validate the Gpt_DeInit() API when Gpt driver is not in INIT state</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21980</t>
+          <t>MCAL-21989</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_Init() API  by passing a valid config pointer but one of the channel id is inavlid(not supported channel)</t>
+          <t>Validate the Gpt_DeInit() API  by calling Gpt_DeInit() API before Gpt_Init() API</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -9466,13 +9466,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test2",
+    "test_app_name": "Gpt_test1",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test2/Gpt_test2.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
       }
     },
    "uart_input": {
@@ -9498,7 +9498,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_PARAM_POINTER" error should be detected and reported to DET module</t>
+          <t>"GPT_E_UNINIT" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr"/>
@@ -9547,32 +9547,32 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26218</t>
+          <t>MCAL-26220</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_Init() API when input config pointer is NULL and it is post build config variant</t>
+          <t>Positive testcase to validate the Gpt_Init() API when input is a valid config pointer and all configuration data is valid</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21980</t>
+          <t>MCAL-23354,MCAL-21985,MCAL-21973,MCAL-22051,MCAL-21975,MCAL-21972,MCAL-22049,MCAL-22068,MCAL-21976,MCAL-21978,MCAL-23357,MCAL-22072,MCAL-22083,MCAL-21974,MCAL-22075,MCAL-23356,MCAL-22050,MCAL-22067,MCAL-22070,MCAL-22057,MCAL-22069,MCAL-23358,MCAL-23352,MCAL-22071,MCAL-21977,MCAL-21979</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_Init() API  by passing a NULL pointer as an argument  when  post build variant is enabled</t>
+          <t>Validate the Gpt_Init() API  by passing a valid config pointer and all configuration data is valid</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
@@ -9629,12 +9629,12 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_PARAM_POINTER" error should be detected and reported to DET module</t>
+          <t>Gpt driver should initialize all the configured channels</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>Fault Injection</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -9659,12 +9659,12 @@
       </c>
       <c r="Q63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr"/>
@@ -9678,32 +9678,32 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26217</t>
+          <t>MCAL-26219</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Re-init requires a prior De-init</t>
+          <t>Negative testcase to validate the Gpt_Init() API when input is a valid config pointer but one of the channel id is inavlid(not supported channel)</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21981,MCAL-21980</t>
+          <t>MCAL-21980</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_Init() API  by passing a NULL pointer as an argument  when  pre compile variant is enabled</t>
+          <t>Validate the Gpt_Init() API  by passing a valid config pointer but one of the channel id is inavlid(not supported channel)</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
@@ -9728,13 +9728,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test1",
+    "test_app_name": "Gpt_test2",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test2/Gpt_test2.out"
       }
     },
    "uart_input": {
@@ -9760,12 +9760,12 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>Gpt driver should be initialized with pre compiled configuration</t>
+          <t>"GPT_E_PARAM_POINTER" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Fault Injection</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>Full,Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="Q64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr"/>
@@ -9809,22 +9809,22 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26216</t>
+          <t>MCAL-26218</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_Init() API when Gpt driver is already in INIT state</t>
+          <t>Negative testcase to validate the Gpt_Init() API when input config pointer is NULL and it is post build config variant</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_Init() API  by calling 2 times continuously</t>
+          <t>Validate the Gpt_Init() API  by passing a NULL pointer as an argument  when  post build variant is enabled</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
@@ -9859,13 +9859,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test1",
+    "test_app_name": "Gpt_test2",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test2/Gpt_test2.out"
       }
     },
    "uart_input": {
@@ -9891,7 +9891,7 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_ALREADY_INITIALIZED" error should be detected and reported to DET module</t>
+          <t>"GPT_E_PARAM_POINTER" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr"/>
@@ -9940,32 +9940,32 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26215</t>
+          <t>MCAL-26217</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_GetVersionInfo() API by passing NULL pointer</t>
+          <t>Re-init requires a prior De-init</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21971</t>
+          <t>MCAL-21981,MCAL-21980</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetVersionInfo() API by passing a NULL pointer as an argument</t>
+          <t>Validate the Gpt_Init() API  by passing a NULL pointer as an argument  when  pre compile variant is enabled</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_PARAM_POINTER" error should be detected and reported to DET module</t>
+          <t>Gpt driver should be initialized with pre compiled configuration</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>Fault Injection</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="Q66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr"/>
@@ -10071,32 +10071,32 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26214</t>
+          <t>MCAL-26216</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Postitive testcase to validate the Gpt_DisableNotification() API</t>
+          <t>Negative testcase to validate the Gpt_Init() API when Gpt driver is already in INIT state</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21779</t>
+          <t>MCAL-21980</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_DisableNotification() API by  checking user notify callback function(User should not notified by this call).</t>
+          <t>Validate the Gpt_Init() API  by calling 2 times continuously</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>Gpt_DisableNotification() API should not report  any errors and disable the timer channel requirested for notifications</t>
+          <t>"GPT_E_ALREADY_INITIALIZED" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Fault Injection</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -10183,12 +10183,12 @@
       </c>
       <c r="Q67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr"/>
@@ -10202,32 +10202,32 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26213</t>
+          <t>MCAL-26215</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Postitive testcase to validate the Gpt_EnableNotification() API</t>
+          <t>Negative testcase to validate the Gpt_GetVersionInfo() API by passing NULL pointer</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21778</t>
+          <t>MCAL-21971</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_EnableNotification() API by  checking user notify callback function( User should be notified by this call).</t>
+          <t>Validate the Gpt_GetVersionInfo() API by passing a NULL pointer as an argument</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>Gpt_EnableNotification() API should not report  any errors and enable the timer channel requirested for notifications</t>
+          <t>"GPT_E_PARAM_POINTER" error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Fault Injection</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="Q68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr"/>
@@ -10333,22 +10333,22 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26212</t>
+          <t>MCAL-26214</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Postitive testcase to validate the Gpt_StopTimer() API</t>
+          <t>Postitive testcase to validate the Gpt_DisableNotification() API</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21777</t>
+          <t>MCAL-21779</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_StopTimer() API by  comparing the timer state which are configured</t>
+          <t>Validate the Gpt_DisableNotification() API by  checking user notify callback function(User should not notified by this call).</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>Gpt_StopTimer() API should not report  any errors and stop the timer channel requested</t>
+          <t>Gpt_DisableNotification() API should not report  any errors and disable the timer channel requirested for notifications</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
@@ -10445,12 +10445,12 @@
       </c>
       <c r="Q69" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr"/>
@@ -10464,32 +10464,32 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26211</t>
+          <t>MCAL-26213</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Postitive testcase to validate the Gpt_StartTimer() API</t>
+          <t>Postitive testcase to validate the Gpt_EnableNotification() API</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Architecture,Architecture,Architecture,Architecture</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21770,MCAL-21776,MCAL-21769,MCAL-21780</t>
+          <t>MCAL-21778</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_StartTimer() API by  comparing the timer state which are configured</t>
+          <t>Validate the Gpt_EnableNotification() API by  checking user notify callback function( User should be notified by this call).</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>Gpt_StartTimer() API should not report  any errors and start the timer channel requested</t>
+          <t>Gpt_EnableNotification() API should not report  any errors and enable the timer channel requirested for notifications</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="Q70" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr"/>
@@ -10595,22 +10595,22 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26210</t>
+          <t>MCAL-26212</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Postitive testcase to validate the Gpt_GetTimeRemaining() API</t>
+          <t>Postitive testcase to validate the Gpt_StopTimer() API</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21775</t>
+          <t>MCAL-21777</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeRemaining() API by reading the time remaining when timer channel is in running state</t>
+          <t>Validate the Gpt_StopTimer() API by  comparing the timer state which are configured</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeRemaining() API should not report  any errors and return time remaining</t>
+          <t>Gpt_StopTimer() API should not report  any errors and stop the timer channel requested</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
@@ -10707,12 +10707,12 @@
       </c>
       <c r="Q71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr"/>
@@ -10726,32 +10726,32 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26209</t>
+          <t>MCAL-26211</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Postitive testcase to validate the Gpt_GetTimeElapsed() API</t>
+          <t>Postitive testcase to validate the Gpt_StartTimer() API</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Architecture,Architecture,Architecture,Architecture</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21774</t>
+          <t>MCAL-21770,MCAL-21776,MCAL-21769,MCAL-21780</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetTimeElapsed() API by reading the time elapsed when timer channel is in running state</t>
+          <t>Validate the Gpt_StartTimer() API by  comparing the timer state which are configured</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetTimeElapsed() API should not report  any errors and return time elapsed</t>
+          <t>Gpt_StartTimer() API should not report  any errors and start the timer channel requested</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
@@ -10838,12 +10838,12 @@
       </c>
       <c r="Q72" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr"/>
@@ -10857,22 +10857,22 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26208</t>
+          <t>MCAL-26210</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Postitive testcase to validate the Gpt_DeInit() API</t>
+          <t>Postitive testcase to validate the Gpt_GetTimeRemaining() API</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21773</t>
+          <t>MCAL-21775</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_DeInit() API by  comparing the timer state which are configured</t>
+          <t>Validate the Gpt_GetTimeRemaining() API by reading the time remaining when timer channel is in running state</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>Gpt_DeInit() API should not report  any errors and deinitialize all the configured channels</t>
+          <t>Gpt_GetTimeRemaining() API should not report  any errors and return time remaining</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
@@ -10969,12 +10969,12 @@
       </c>
       <c r="Q73" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr"/>
@@ -10988,22 +10988,22 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26207</t>
+          <t>MCAL-26209</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Postitive testcase to validate the Gpt_Init() API when input pointer is NULL and pre compile variant is enabled</t>
+          <t>Postitive testcase to validate the Gpt_GetTimeElapsed() API</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21772</t>
+          <t>MCAL-21774</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_Init() API by  comparing the timer state which are configured</t>
+          <t>Validate the Gpt_GetTimeElapsed() API by reading the time elapsed when timer channel is in running state</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>Gpt_Init() API should not report  any errors and initialize all the pre compile configured channels</t>
+          <t>Gpt_GetTimeElapsed() API should not report  any errors and return time elapsed</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
@@ -11100,12 +11100,12 @@
       </c>
       <c r="Q74" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr"/>
@@ -11119,32 +11119,32 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26206</t>
+          <t>MCAL-26208</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Postitive testcase to validate the Gpt_Init() API</t>
+          <t>Postitive testcase to validate the Gpt_DeInit() API</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Design,Architecture,Architecture,Architecture</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22081,MCAL-21768,MCAL-21772,MCAL-21781</t>
+          <t>MCAL-21773</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_Init() API by  comparing the timer state which are configured</t>
+          <t>Validate the Gpt_DeInit() API by  comparing the timer state which are configured</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>Gpt_Init() API should not report  any errors and initialize all the configured channels</t>
+          <t>Gpt_DeInit() API should not report  any errors and deinitialize all the configured channels</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="Q75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr"/>
@@ -11250,22 +11250,22 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26205</t>
+          <t>MCAL-26207</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Postitive testcase to validate the Gpt_GetVersionInfo() API</t>
+          <t>Postitive testcase to validate the Gpt_Init() API when input pointer is NULL and pre compile variant is enabled</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21771</t>
+          <t>MCAL-21772</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_GetVersionInfo() API by comparing the versions came out of OUT parameter when a valid pointer is passed as an argument</t>
+          <t>Validate the Gpt_Init() API by  comparing the timer state which are configured</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>Gpt_GetVersionInfo() API should not report  any errors and return all versions details</t>
+          <t>Gpt_Init() API should not report  any errors and initialize all the pre compile configured channels</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>Full,Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="Q76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S76" s="3" t="inlineStr"/>
@@ -11381,32 +11381,32 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26198</t>
+          <t>MCAL-26206</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Negative test case to validate the Gpt_Init() API when input is a non NULL_PTR in pre-compile build variant</t>
+          <t>Postitive testcase to validate the Gpt_Init() API</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Architecture,Architecture,Architecture</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21977</t>
+          <t>MCAL-22081,MCAL-21768,MCAL-21772,MCAL-21781</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -11416,12 +11416,12 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>Validate the time elapsed when timer 0 is enabled for one shot mode for 100s timeout and timer is in initialized state</t>
+          <t>Validate the Gpt_Init() API by  comparing the timer state which are configured</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>GPT_E_PARAM_POINTER error should be detected and reported to DET module</t>
+          <t>Gpt_Init() API should not report  any errors and initialize all the configured channels</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="Q77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R77" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S77" s="3" t="inlineStr"/>
@@ -11512,32 +11512,32 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26180</t>
+          <t>MCAL-26205</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Validate timer 2 with XTAL as clock source in continuous</t>
+          <t>Postitive testcase to validate the Gpt_GetVersionInfo() API</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21425</t>
+          <t>MCAL-21771</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>Test timer 2 in one shot mode for 1s timeout with XTAL as clock source &amp; notification event enabled</t>
+          <t>Validate the Gpt_GetVersionInfo() API by comparing the versions came out of OUT parameter when a valid pointer is passed as an argument</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
@@ -11562,13 +11562,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test9",
+    "test_app_name": "Gpt_test1",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test9/Gpt_test9.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
       }
     },
    "uart_input": {
@@ -11594,7 +11594,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>GPT timer  2 should run with configured value and receive notification event only once</t>
+          <t>Gpt_GetVersionInfo() API should not report  any errors and return all versions details</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
@@ -11624,12 +11624,12 @@
       </c>
       <c r="Q78" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S78" s="3" t="inlineStr"/>
@@ -11643,32 +11643,32 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26179</t>
+          <t>MCAL-26198</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Validate timer 2 with XTAL as clock source in one shot</t>
+          <t>Negative test case to validate the Gpt_Init() API when input is a non NULL_PTR in pre-compile build variant</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21425</t>
+          <t>MCAL-21977</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -11678,12 +11678,12 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>Test timer 2 in one shot mode for 1s timeout with XTAL as clock source &amp; notification event enabled</t>
+          <t>Validate the time elapsed when timer 0 is enabled for one shot mode for 100s timeout and timer is in initialized state</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
@@ -11693,13 +11693,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test8",
+    "test_app_name": "Gpt_test1",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test8/Gpt_test8.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test1/Gpt_test1.out"
       }
     },
    "uart_input": {
@@ -11725,7 +11725,7 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>GPT timer  2 should run with configured value and receive notification event only once</t>
+          <t>GPT_E_PARAM_POINTER error should be detected and reported to DET module</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
@@ -11755,12 +11755,12 @@
       </c>
       <c r="Q79" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R79" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr"/>
@@ -11774,22 +11774,22 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26178</t>
+          <t>MCAL-26180</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Validate timer 2 with INTOSC2 as clock source in continuous</t>
+          <t>Validate timer 2 with XTAL as clock source in continuous</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>Test timer 2 in one shot mode for 1s timeout with INTOSC2 as clock source &amp; notification event enabled</t>
+          <t>Test timer 2 in one shot mode for 1s timeout with XTAL as clock source &amp; notification event enabled</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
@@ -11824,13 +11824,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test11",
+    "test_app_name": "Gpt_test9",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test11/Gpt_test11.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test9/Gpt_test9.out"
       }
     },
    "uart_input": {
@@ -11856,7 +11856,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>GPT timer 2 should run with configured value and receive notification event only once</t>
+          <t>GPT timer  2 should run with configured value and receive notification event only once</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
@@ -11886,12 +11886,12 @@
       </c>
       <c r="Q80" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S80" s="3" t="inlineStr"/>
@@ -11905,32 +11905,32 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26177</t>
+          <t>MCAL-26179</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Validate timer 2 with INTOSC2 as clock source in one shot</t>
+          <t>Validate timer 2 with XTAL as clock source in one shot</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Requirement,Requirement</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21433,MCAL-21425</t>
+          <t>MCAL-21425</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>Test timer 2 in one shot mode for 1s timeout with INTOSC2 as clock source &amp; notification event enabled</t>
+          <t>Test timer 2 in one shot mode for 1s timeout with XTAL as clock source &amp; notification event enabled</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
@@ -11955,13 +11955,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test10",
+    "test_app_name": "Gpt_test8",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test10/Gpt_test10.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test8/Gpt_test8.out"
       }
     },
    "uart_input": {
@@ -11987,7 +11987,7 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>GPT timer 2 should run with configured value and receive notification event only once</t>
+          <t>GPT timer  2 should run with configured value and receive notification event only once</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
@@ -12017,12 +12017,12 @@
       </c>
       <c r="Q81" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr"/>
@@ -12036,32 +12036,32 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26176</t>
+          <t>MCAL-26178</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Validate timer 2 with INTOSC1 as clock source in continuous</t>
+          <t>Validate timer 2 with INTOSC2 as clock source in continuous</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Requirement,Requirement</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21433,MCAL-21425</t>
+          <t>MCAL-21425</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>Test timer 2 in one shot mode for 1s timeout with INTOSC1 as clock source &amp; notification event enabled</t>
+          <t>Test timer 2 in one shot mode for 1s timeout with INTOSC2 as clock source &amp; notification event enabled</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
@@ -12086,13 +12086,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test7",
+    "test_app_name": "Gpt_test11",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test7/Gpt_test7.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test11/Gpt_test11.out"
       }
     },
    "uart_input": {
@@ -12138,7 +12138,7 @@
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>Full,Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P82" s="3" t="inlineStr">
@@ -12148,12 +12148,12 @@
       </c>
       <c r="Q82" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S82" s="3" t="inlineStr"/>
@@ -12167,22 +12167,22 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26175</t>
+          <t>MCAL-26177</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Validate timer 2 with INTOSC1 as clock source in one shot</t>
+          <t>Validate timer 2 with INTOSC2 as clock source in one shot</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>Test timer 2 in one shot mode for 1s timeout with INTOSC1 as clock source &amp; notification event enabled</t>
+          <t>Test timer 2 in one shot mode for 1s timeout with INTOSC2 as clock source &amp; notification event enabled</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
@@ -12217,13 +12217,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test6",
+    "test_app_name": "Gpt_test10",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test6/Gpt_test6.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test10/Gpt_test10.out"
       }
     },
    "uart_input": {
@@ -12279,12 +12279,12 @@
       </c>
       <c r="Q83" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R83" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S83" s="3" t="inlineStr"/>
@@ -12298,32 +12298,32 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>MCAL-26270</t>
+          <t>MCAL-26176</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Negative testcase to validate the Gpt_DisableNotification() API when notification callback pointer is NULL</t>
+          <t>Validate timer 2 with INTOSC1 as clock source in continuous</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Requirement,Requirement</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>MCAL-22033</t>
+          <t>MCAL-21433,MCAL-21425</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -12333,12 +12333,12 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>Validate the Gpt_DisableNotification() API  by calling Gpt_DisableNotification() API when notification callback pointer is NULL</t>
+          <t>Test timer 2 in one shot mode for 1s timeout with INTOSC1 as clock source &amp; notification event enabled</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
@@ -12348,13 +12348,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test4",
+    "test_app_name": "Gpt_test7",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test4/Gpt_test4.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test7/Gpt_test7.out"
       }
     },
    "uart_input": {
@@ -12380,12 +12380,12 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>"GPT_E_PARAM_CHANNEL"  error should be detected and reported to DET module</t>
+          <t>GPT timer 2 should run with configured value and receive notification event only once</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>Fault Injection</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="Q84" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S84" s="3" t="inlineStr"/>
@@ -12429,22 +12429,22 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27002</t>
+          <t>MCAL-28005</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Tests</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Tests</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27017</t>
+          <t>MCAL-26175</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Positive test case to validate the Gpt_EnableNotification() API in continuous mode</t>
+          <t>Validate timer 2 with INTOSC1 as clock source in one shot</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>MCAL-21433,MCAL-21432</t>
+          <t>MCAL-21433,MCAL-21425</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>Gpt_EnableNotification() API should not report  any errors and enable the timer channel requested for notifications in continuous mode</t>
+          <t>Test timer 2 in one shot mode for 1s timeout with INTOSC1 as clock source &amp; notification event enabled</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
@@ -12479,13 +12479,13 @@
     "core_os": [
       "c29xx_cpu1"
     ],
-    "test_app_name": "Gpt_test3",
+    "test_app_name": "Gpt_test6",
     "scripts": "generic_mcu_json.py",
     "no_of_cores": 1,
     "skip_duplicate": "true",
     "app_image": {
       "image_1": {
-        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test11/Gpt_test3.out"
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Gpt_test6/Gpt_test6.out"
       }
     },
    "uart_input": {
@@ -12511,7 +12511,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>GPT timers 0,1 &amp; 2 should run with configured value and receive notification event</t>
+          <t>GPT timer 2 should run with configured value and receive notification event only once</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
@@ -12541,12 +12541,12 @@
       </c>
       <c r="Q85" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27005</t>
+          <t>MCAL-28004</t>
         </is>
       </c>
       <c r="R85" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Automated Test Run</t>
+          <t>F29H85xMCAL_01.01.00 : GPT- Automated Test Run</t>
         </is>
       </c>
       <c r="S85" s="3" t="inlineStr"/>
@@ -12557,2384 +12557,8 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26897</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>Postitive testcase to validate interrupt generation Timeout</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>Requirement,Requirement</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21429,MCAL-21430</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I86" s="3" t="inlineStr">
-        <is>
-          <t>Test timer 0,1 and 2 for 1 sec timeout with SYSCLK as clock source &amp; notification event enabled</t>
-        </is>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K86" s="3" t="inlineStr">
-        <is>
-          <t>GPT timers 0,1 &amp; 2 should run with configured value and receive notification event only once</t>
-        </is>
-      </c>
-      <c r="L86" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M86" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N86" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O86" s="3" t="inlineStr">
-        <is>
-          <t>Full,Regression</t>
-        </is>
-      </c>
-      <c r="P86" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q86" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R86" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S86" s="3" t="inlineStr"/>
-      <c r="T86" s="3" t="inlineStr"/>
-      <c r="U86" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26711</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>GPT reports development errors and runtime/production errors</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21968,MCAL-21964,MCAL-22034,MCAL-21970,MCAL-21962,MCAL-21961,MCAL-21969,MCAL-21967,MCAL-21963,MCAL-22042,MCAL-21965,MCAL-21966</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I87" s="3" t="inlineStr">
-        <is>
-          <t>Verify if Gpt  driver reports development errors and runtime/production errors and use Det-ReportError service and Dem_SetEventStatus</t>
-        </is>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K87" s="3" t="inlineStr">
-        <is>
-          <t>Verify Gpt reports development errors and runtime/production errors</t>
-        </is>
-      </c>
-      <c r="L87" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M87" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N87" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O87" s="3" t="inlineStr">
-        <is>
-          <t>Full,Sanity</t>
-        </is>
-      </c>
-      <c r="P87" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q87" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R87" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S87" s="3" t="inlineStr"/>
-      <c r="T87" s="3" t="inlineStr"/>
-      <c r="U87" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26710</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>Gpt Module : File Structure</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>Design,Design,Design,Design</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21954,MCAL-21955,MCAL-22063,MCAL-21953</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I88" s="3" t="inlineStr">
-        <is>
-          <t>Verify the Gpt driver module file structure is maintained as per autosar SWS document</t>
-        </is>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K88" s="3" t="inlineStr">
-        <is>
-          <t>Verify this test case Manually through code review of  files and folder structure which holds Gpt driver module config details and code implementatation and hardware registers information</t>
-        </is>
-      </c>
-      <c r="L88" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M88" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N88" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O88" s="3" t="inlineStr">
-        <is>
-          <t>Full,Sanity</t>
-        </is>
-      </c>
-      <c r="P88" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q88" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R88" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S88" s="3" t="inlineStr"/>
-      <c r="T88" s="3" t="inlineStr"/>
-      <c r="U88" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26411</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>Testcase to capture ECUC Requirements</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-22040,MCAL-23355,MCAL-22049,MCAL-22038,MCAL-22058,MCAL-22071,MCAL-22074,MCAL-22059,MCAL-22055,MCAL-22067,MCAL-22064,MCAL-22054,MCAL-23356,MCAL-22037,MCAL-22066,MCAL-22045,MCAL-22065,MCAL-22073,MCAL-22068,MCAL-23348,MCAL-22069,MCAL-22046,MCAL-23351,MCAL-22050,MCAL-22041,MCAL-22060,MCAL-22062,MCAL-22053,MCAL-22084,MCAL-21957,MCAL-22035,MCAL-23349,MCAL-22052,MCAL-22044,MCAL-22077,MCAL-21956,MCAL-22086,MCAL-22047,MCAL-23353,MCAL-22085,MCAL-22057,MCAL-22078,MCAL-22061,MCAL-22039,MCAL-21959,MCAL-22056,MCAL-22048,MCAL-22036,MCAL-23358,MCAL-23170</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr">
-        <is>
-          <t>Verify If the generated tresos configuration files Gpt_Cfg.h and Gpt_PBCfg.c files have data related to all ECUC Requirements</t>
-        </is>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>Manual verification</t>
-        </is>
-      </c>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verify this test case Manually through code review of generated configuration files which holds GPT driver module config details. </t>
-        </is>
-      </c>
-      <c r="L89" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M89" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N89" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O89" s="3" t="inlineStr">
-        <is>
-          <t>Full,Sanity</t>
-        </is>
-      </c>
-      <c r="P89" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q89" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R89" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S89" s="3" t="inlineStr"/>
-      <c r="T89" s="3" t="inlineStr"/>
-      <c r="U89" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26165</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>Simultanuous Timers Test In Continuous mode for 10ms Timeout</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>Requirement,Requirement</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21431,MCAL-21424</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I90" s="3" t="inlineStr">
-        <is>
-          <t>Test timer 0,1 and 2 in continuous mode for 10ms timeout with SYSCLK as clock source &amp; notification event enabled</t>
-        </is>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K90" s="3" t="inlineStr">
-        <is>
-          <t>GPT timers 0,1 &amp; 2 should run with configured value and receive notification event</t>
-        </is>
-      </c>
-      <c r="L90" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M90" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N90" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O90" s="3" t="inlineStr">
-        <is>
-          <t>Full,Regression</t>
-        </is>
-      </c>
-      <c r="P90" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q90" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R90" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S90" s="3" t="inlineStr"/>
-      <c r="T90" s="3" t="inlineStr"/>
-      <c r="U90" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26166</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>Simultanuous Timers Test In Continuous mode for 100ms Timeout</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>Requirement,Requirement</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21431,MCAL-21424</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I91" s="3" t="inlineStr">
-        <is>
-          <t>Test timer 0,1 and 2 in continuous mode for 100ms timeout with SYSCLK as clock source &amp; notification event enabled</t>
-        </is>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K91" s="3" t="inlineStr">
-        <is>
-          <t>GPT timers 0,1 &amp; 2 should run with configured value and receive notification event</t>
-        </is>
-      </c>
-      <c r="L91" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M91" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N91" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O91" s="3" t="inlineStr">
-        <is>
-          <t>Full,Regression</t>
-        </is>
-      </c>
-      <c r="P91" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q91" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R91" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S91" s="3" t="inlineStr"/>
-      <c r="T91" s="3" t="inlineStr"/>
-      <c r="U91" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26167</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>Simultanuous Timers Test In Continuous mode for 1s Timeout</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>Requirement,Requirement</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21431,MCAL-21424</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I92" s="3" t="inlineStr">
-        <is>
-          <t>Test timer 0,1 and 2 in continuous mode for 1s timeout with SYSCLK as clock source &amp; notification event enabled</t>
-        </is>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K92" s="3" t="inlineStr">
-        <is>
-          <t>GPT timers 0,1 &amp; 2 should run with configured value and receive notification event</t>
-        </is>
-      </c>
-      <c r="L92" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M92" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N92" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O92" s="3" t="inlineStr">
-        <is>
-          <t>Full,Regression</t>
-        </is>
-      </c>
-      <c r="P92" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q92" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R92" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S92" s="3" t="inlineStr"/>
-      <c r="T92" s="3" t="inlineStr"/>
-      <c r="U92" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26168</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>Simultanuous Timers Test In Continuous mode for Max. Tick Count</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21424</t>
-        </is>
-      </c>
-      <c r="G93" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="inlineStr">
-        <is>
-          <t>Test timer 0,1 and 2 in continuous mode for max tick count(0xFFFFFFFF) timeout with SYSCLK as clock source &amp; notification event enabled</t>
-        </is>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K93" s="3" t="inlineStr">
-        <is>
-          <t>GPT timers 0,1 &amp; 2 should run with configured value and receive notification event</t>
-        </is>
-      </c>
-      <c r="L93" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M93" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N93" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O93" s="3" t="inlineStr">
-        <is>
-          <t>Full,Regression</t>
-        </is>
-      </c>
-      <c r="P93" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q93" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R93" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S93" s="3" t="inlineStr"/>
-      <c r="T93" s="3" t="inlineStr"/>
-      <c r="U93" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26169</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>Simultanuous Timers Test In One Shot  mode for 10ms Timeout</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21424</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I94" s="3" t="inlineStr">
-        <is>
-          <t>Test timer 0,1 and 2 in one shot mode for 10ms timeout with SYSCLK as clock source &amp; notification event enabled</t>
-        </is>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K94" s="3" t="inlineStr">
-        <is>
-          <t>GPT timers 0,1 &amp; 2 should run with configured value and receive notification event only once</t>
-        </is>
-      </c>
-      <c r="L94" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M94" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N94" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O94" s="3" t="inlineStr">
-        <is>
-          <t>Full,Regression</t>
-        </is>
-      </c>
-      <c r="P94" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q94" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R94" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S94" s="3" t="inlineStr"/>
-      <c r="T94" s="3" t="inlineStr"/>
-      <c r="U94" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26170</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>Simultanuous Timers Test In One Shot mode for 100ms Timeout</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21424</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I95" s="3" t="inlineStr">
-        <is>
-          <t>Test timer 0,1 and 2 in one shot mode for 100ms timeout with SYSCLK as clock source &amp; notification event enabled</t>
-        </is>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K95" s="3" t="inlineStr">
-        <is>
-          <t>GPT timers 0,1 &amp; 2 should run with configured value and receive notification event only once</t>
-        </is>
-      </c>
-      <c r="L95" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M95" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N95" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O95" s="3" t="inlineStr">
-        <is>
-          <t>Full,Regression</t>
-        </is>
-      </c>
-      <c r="P95" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q95" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R95" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S95" s="3" t="inlineStr"/>
-      <c r="T95" s="3" t="inlineStr"/>
-      <c r="U95" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26171</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>Simultanuous Timers Test In One Shot mode for 1s Timeout</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21424</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I96" s="3" t="inlineStr">
-        <is>
-          <t>Test timer 0,1 and 2 in one shot mode for 1s timeout with SYSCLK as clock source &amp; notification event enabled</t>
-        </is>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K96" s="3" t="inlineStr">
-        <is>
-          <t>GPT timers 0,1 &amp; 2 should run with configured value and receive notification event only once</t>
-        </is>
-      </c>
-      <c r="L96" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M96" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N96" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O96" s="3" t="inlineStr">
-        <is>
-          <t>Full,Regression</t>
-        </is>
-      </c>
-      <c r="P96" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q96" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R96" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S96" s="3" t="inlineStr"/>
-      <c r="T96" s="3" t="inlineStr"/>
-      <c r="U96" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26172</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>Simultanuous Timers Test In One Shot mode for Max. Tick Count</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21424</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I97" s="3" t="inlineStr">
-        <is>
-          <t>Test timer 0,1 and 2 in one shot mode for max tick count(0xFFFFFFFF) timeout with SYSCLK as clock source &amp; notification event enabled</t>
-        </is>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="inlineStr">
-        <is>
-          <t>GPT timers 0,1 &amp; 2 should run with configured value and receive notification event only once</t>
-        </is>
-      </c>
-      <c r="L97" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M97" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N97" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O97" s="3" t="inlineStr">
-        <is>
-          <t>Full,Regression</t>
-        </is>
-      </c>
-      <c r="P97" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q97" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R97" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S97" s="3" t="inlineStr"/>
-      <c r="T97" s="3" t="inlineStr"/>
-      <c r="U97" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26173</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>Mixed modes and Simultanuous Timers Test1 for 1s timeout</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>Requirement,Requirement,Requirement,Requirement</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21428,MCAL-21432,MCAL-21427,MCAL-21424</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I98" s="3" t="inlineStr">
-        <is>
-          <t>Test timer 1 in continuous mode &amp; timer 2 in one shot more for 1sec timeout with SYSCLK as clock source &amp; notification event enabled</t>
-        </is>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K98" s="3" t="inlineStr">
-        <is>
-          <t>GPT timers 0,1 &amp; 2 should run with configured value and receive notification event only once</t>
-        </is>
-      </c>
-      <c r="L98" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M98" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N98" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O98" s="3" t="inlineStr">
-        <is>
-          <t>Full,Regression</t>
-        </is>
-      </c>
-      <c r="P98" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q98" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R98" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S98" s="3" t="inlineStr"/>
-      <c r="T98" s="3" t="inlineStr"/>
-      <c r="U98" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26174</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>Mixed modes and Simultanuous Timers Test2 for 1s timeout</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>Requirement,Requirement,Requirement,Requirement</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21427,MCAL-21428,MCAL-21432,MCAL-21424</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I99" s="3" t="inlineStr">
-        <is>
-          <t>Test timer 2 in continuous mode &amp; timer 0 in one shot more for 1sec timeout with SYSCLK as clock source &amp; notification event enabled</t>
-        </is>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K99" s="3" t="inlineStr">
-        <is>
-          <t>GPT timers 0,1 &amp; 2 should run with configured value and receive notification event only once</t>
-        </is>
-      </c>
-      <c r="L99" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M99" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N99" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O99" s="3" t="inlineStr">
-        <is>
-          <t>Full,Regression</t>
-        </is>
-      </c>
-      <c r="P99" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q99" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R99" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S99" s="3" t="inlineStr"/>
-      <c r="T99" s="3" t="inlineStr"/>
-      <c r="U99" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26203</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>The GPT driver shall use the time unit ticks for all API services which are related to GPT timer channels</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21421</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr">
-        <is>
-          <t>Validate the Gpt timer channel 0 notification enable &amp; disable sequence when the timer running in continuous mode</t>
-        </is>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>Ensure all Gpt timers channel related api's uses unit ticks through code review</t>
-        </is>
-      </c>
-      <c r="L100" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M100" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N100" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O100" s="3" t="inlineStr">
-        <is>
-          <t>Full,Sanity</t>
-        </is>
-      </c>
-      <c r="P100" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q100" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R100" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S100" s="3" t="inlineStr"/>
-      <c r="T100" s="3" t="inlineStr"/>
-      <c r="U100" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26237</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>Validate the Gpt_GetTimeElapsed() API  whether it is fully reentrant</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-21995</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr">
-        <is>
-          <t>Validate the Gpt_GetTimeElapsed() API  by calling in two different threads</t>
-        </is>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr">
-        <is>
-          <t>Check manually in the driver code whether it handles the reentrant</t>
-        </is>
-      </c>
-      <c r="L101" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M101" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N101" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O101" s="3" t="inlineStr">
-        <is>
-          <t>Full,Regression</t>
-        </is>
-      </c>
-      <c r="P101" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q101" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R101" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S101" s="3" t="inlineStr"/>
-      <c r="T101" s="3" t="inlineStr"/>
-      <c r="U101" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26250</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>Validate the Gpt_GetTimeRemaining() API  whether it is fully reentrant</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-22003</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="inlineStr">
-        <is>
-          <t>Validate the Gpt_GetTimeRemaining() API  by calling in two different threads</t>
-        </is>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>Check manually in the driver code whether it handles the reentrant</t>
-        </is>
-      </c>
-      <c r="L102" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M102" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N102" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O102" s="3" t="inlineStr">
-        <is>
-          <t>Full,Regression</t>
-        </is>
-      </c>
-      <c r="P102" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q102" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R102" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S102" s="3" t="inlineStr"/>
-      <c r="T102" s="3" t="inlineStr"/>
-      <c r="U102" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26261</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>Validate the Gpt_StopTimer() API  whether it is fully reentrant</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-22019</t>
-        </is>
-      </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t>Validate the Gpt_StopTimer() API  by calling in two different threads</t>
-        </is>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="inlineStr">
-        <is>
-          <t>Check manually in the driver code whether it handles the reentrant</t>
-        </is>
-      </c>
-      <c r="L103" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M103" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N103" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O103" s="3" t="inlineStr">
-        <is>
-          <t>Full,Regression</t>
-        </is>
-      </c>
-      <c r="P103" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q103" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R103" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S103" s="3" t="inlineStr"/>
-      <c r="T103" s="3" t="inlineStr"/>
-      <c r="U103" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26256</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>Validate the Gpt_StartTimer() API  whether it is fully reentrant</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-22009</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I104" s="3" t="inlineStr">
-        <is>
-          <t>Validate the Gpt_StartTimer() API  by calling in two different threads</t>
-        </is>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K104" s="3" t="inlineStr">
-        <is>
-          <t>Check manually in the driver code whether it handles the reentrant</t>
-        </is>
-      </c>
-      <c r="L104" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M104" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N104" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O104" s="3" t="inlineStr">
-        <is>
-          <t>Full,Regression</t>
-        </is>
-      </c>
-      <c r="P104" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q104" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R104" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S104" s="3" t="inlineStr"/>
-      <c r="T104" s="3" t="inlineStr"/>
-      <c r="U104" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26272</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>Validate the Gpt_DisableNotification() API  whether it is fully reentrant</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-22029</t>
-        </is>
-      </c>
-      <c r="G105" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I105" s="3" t="inlineStr">
-        <is>
-          <t>Validate the Gpt_DisableNotification() API  by calling in two different threads</t>
-        </is>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K105" s="3" t="inlineStr">
-        <is>
-          <t>Check manually in the driver code whether it handles the reentrant</t>
-        </is>
-      </c>
-      <c r="L105" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M105" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N105" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O105" s="3" t="inlineStr">
-        <is>
-          <t>Full,Regression</t>
-        </is>
-      </c>
-      <c r="P105" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q105" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R105" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S105" s="3" t="inlineStr"/>
-      <c r="T105" s="3" t="inlineStr"/>
-      <c r="U105" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26266</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>Validate the Gpt_EnableNotification() API  whether it is fully reentrant</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-22023</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="I106" s="3" t="inlineStr">
-        <is>
-          <t>Validate the Gpt_EnableNotification() API  by calling in two different threads</t>
-        </is>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K106" s="3" t="inlineStr">
-        <is>
-          <t>Check manually in the driver code whether it handles the reentrant</t>
-        </is>
-      </c>
-      <c r="L106" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M106" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N106" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O106" s="3" t="inlineStr">
-        <is>
-          <t>Full,Regression</t>
-        </is>
-      </c>
-      <c r="P106" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q106" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R106" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S106" s="3" t="inlineStr"/>
-      <c r="T106" s="3" t="inlineStr"/>
-      <c r="U106" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27027</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>Manual Test To verify Gpt Header File inclusions to satisfy AUTOSAR 4.3.1 requirements</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>Architecture</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27023</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="I107" s="3" t="inlineStr">
-        <is>
-          <t>Manually verify all header files required for Gpt driver are included correctly as per Autosar 4.3.1 requirements</t>
-        </is>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K107" s="3" t="inlineStr">
-        <is>
-          <t>All header files required for Gpt driver are included correctly as per Autosar 4.3.1 requirements</t>
-        </is>
-      </c>
-      <c r="L107" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M107" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N107" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O107" s="3" t="inlineStr">
-        <is>
-          <t>Full,Sanity</t>
-        </is>
-      </c>
-      <c r="P107" s="3" t="inlineStr">
-        <is>
-          <t>Gpt</t>
-        </is>
-      </c>
-      <c r="Q107" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R107" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S107" s="3" t="inlineStr"/>
-      <c r="T107" s="3" t="inlineStr"/>
-      <c r="U107" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27032</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>Manual Test To Verify AUTOSAR 4.3.1 BSW and SPAL requirements</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-12327,MCAL-12305,MCAL-25467,MCAL-12412,MCAL-12411,MCAL-12410,MCAL-12389,MCAL-12374,MCAL-12355,MCAL-12309,MCAL-12448,MCAL-12395,MCAL-12379,MCAL-12375,MCAL-12446,MCAL-25460,MCAL-25458,MCAL-12345,MCAL-12341,MCAL-12356,MCAL-12338,MCAL-12335,MCAL-12333,MCAL-12332,MCAL-12427,MCAL-12421,MCAL-12418,MCAL-25456,MCAL-12376,MCAL-12340,MCAL-12316,MCAL-12312,MCAL-12310,MCAL-12361,MCAL-12399,MCAL-25455,MCAL-25471,MCAL-25469,MCAL-25461,MCAL-12337,MCAL-12334,MCAL-12323,MCAL-12303,MCAL-12425,MCAL-12447,MCAL-12438,MCAL-12444,MCAL-12357,MCAL-12330,MCAL-25464</t>
-        </is>
-      </c>
-      <c r="G108" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="I108" s="3" t="inlineStr">
-        <is>
-          <t>Manually verify all Modules Design requirements are satisfying the AUTOSAR BSW and SPAL requirements</t>
-        </is>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K108" s="3" t="inlineStr">
-        <is>
-          <t>Module Design requirements are satisfying the AUTOSAR BSW and SPAL requirements</t>
-        </is>
-      </c>
-      <c r="L108" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M108" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N108" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O108" s="3" t="inlineStr">
-        <is>
-          <t>Full,Sanity</t>
-        </is>
-      </c>
-      <c r="P108" s="3" t="inlineStr">
-        <is>
-          <t>Can,Dio,Gpt,Mcu,Port</t>
-        </is>
-      </c>
-      <c r="Q108" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R108" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S108" s="3" t="inlineStr"/>
-      <c r="T108" s="3" t="inlineStr"/>
-      <c r="U108" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27003</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Tests</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27033</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>Manual Test To Verify AUTOSAR 4.3.1 Functional requirement</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>Requirement,Requirement,Requirement,Requirement</t>
-        </is>
-      </c>
-      <c r="F109" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-26907,MCAL-26985,MCAL-26908,MCAL-27018</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>Qualification</t>
-        </is>
-      </c>
-      <c r="I109" s="3" t="inlineStr">
-        <is>
-          <t>Manually verify AUTOSAR 4.3.1 Functional requirement.</t>
-        </is>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K109" s="3" t="inlineStr">
-        <is>
-          <t>AUTOSAR 4.3.1 Requirements are satisfied</t>
-        </is>
-      </c>
-      <c r="L109" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M109" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N109" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O109" s="3" t="inlineStr">
-        <is>
-          <t>Full,Sanity</t>
-        </is>
-      </c>
-      <c r="P109" s="3" t="inlineStr">
-        <is>
-          <t>Port</t>
-        </is>
-      </c>
-      <c r="Q109" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27004</t>
-        </is>
-      </c>
-      <c r="R109" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.00.00 : GPT- Manual Test Run</t>
-        </is>
-      </c>
-      <c r="S109" s="3" t="inlineStr"/>
-      <c r="T109" s="3" t="inlineStr"/>
-      <c r="U109" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:U109"/>
+  <autoFilter ref="A1:U85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
